--- a/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,55 +656,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>44957</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44592</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43861</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43496</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43131</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42766</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -714,36 +714,39 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4527200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4393000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4099900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2651400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>622700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>330500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>151500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>60800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,36 +756,39 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1070700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1100500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1054600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>822000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>115400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,36 +798,39 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3456500</v>
+      </c>
+      <c r="E10" s="3">
         <v>3292500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3045300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1829400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>507300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>269500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>120700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,9 +840,12 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,35 +861,36 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>783600</v>
+      </c>
+      <c r="E12" s="3">
         <v>774100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>363000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>164100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>67100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9200</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,9 +900,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,24 +942,27 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>125500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>9800</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,15 +978,18 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1004,9 +1026,12 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,35 +1044,36 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4001900</v>
+      </c>
+      <c r="E17" s="3">
         <v>4147500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3036300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1991500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>610000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>324400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>156300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>60800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1057,35 +1083,38 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>525300</v>
+      </c>
+      <c r="E18" s="3">
         <v>245400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1063600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>659800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>12700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
+      <c r="K18" s="3">
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
@@ -1096,9 +1125,12 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,35 +1146,36 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E20" s="3">
         <v>3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>18200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,36 +1185,39 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>936800</v>
+      </c>
+      <c r="E21" s="3">
         <v>331600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1149800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>706900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>42800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,9 +1227,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1230,36 +1269,39 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>832300</v>
+      </c>
+      <c r="E23" s="3">
         <v>249300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1101600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>678000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1311,39 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>194900</v>
+      </c>
+      <c r="E24" s="3">
         <v>145600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-274000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,9 +1353,12 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,35 +1395,38 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E26" s="3">
         <v>103700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1375600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>672300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
+      <c r="K26" s="3">
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
@@ -1386,36 +1437,39 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E27" s="3">
         <v>103700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1375100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>671500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21800</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,9 +1479,12 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,36 +1647,39 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-307000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-18200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1620,36 +1689,39 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E33" s="3">
         <v>103700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1375100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>671500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21800</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,9 +1731,12 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,36 +1773,39 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E35" s="3">
         <v>103700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1375100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>671500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21800</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,41 +1815,44 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>44957</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44592</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43861</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43496</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43131</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42766</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1781,9 +1862,12 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,32 +1901,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1558300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1086800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1062800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2240300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>283100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,33 +1940,36 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5404200</v>
+      </c>
+      <c r="E42" s="3">
         <v>4325800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4356400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2004400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>572100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>112800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>103100</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1893,33 +1982,36 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>536100</v>
+      </c>
+      <c r="E43" s="3">
         <v>557400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>419700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>294700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1932,9 +2024,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,33 +2066,36 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>427700</v>
+      </c>
+      <c r="E45" s="3">
         <v>386300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>344900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>253400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>119900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>36700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2010,33 +2108,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7926200</v>
+      </c>
+      <c r="E46" s="3">
         <v>6356400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6183800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4792900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1095500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>276700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2049,27 +2150,30 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>435300</v>
+      </c>
+      <c r="E47" s="3">
         <v>491000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>423500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>41500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2085,36 +2189,39 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E48" s="3">
         <v>333700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>318300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>247600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2127,24 +2234,27 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>379500</v>
+      </c>
+      <c r="E49" s="3">
         <v>179300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,15 +2270,18 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,33 +2360,36 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>836100</v>
+      </c>
+      <c r="E52" s="3">
         <v>767600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>598100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>191700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>56600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18800</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,9 +2402,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,33 +2444,36 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9929800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8128100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7551300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5298000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1289800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>354600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>215000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,9 +2486,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,32 +2525,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>14400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,9 +2564,12 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2473,33 +2606,36 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1752000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1724200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1571800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1251300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>332200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>147400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>65800</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2512,33 +2648,36 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1762200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1738600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1579700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1260000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>333800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>152300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68500</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2551,9 +2690,12 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2570,11 +2712,11 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>14900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2590,33 +2732,36 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E62" s="3">
         <v>182800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>191600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>177300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>122100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2629,9 +2774,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,33 +2900,36 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1910400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1921500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1771300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1437200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>455900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>202500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2785,9 +2942,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2899,13 +3066,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>159600</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>159600</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>159600</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2919,9 +3086,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,33 +3128,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2789300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2151800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2048100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>672500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-32700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,9 +3170,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,33 +3296,36 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8019400</v>
+      </c>
+      <c r="E76" s="3">
         <v>6206600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5780000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3860800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>833900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-7500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-26700</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3153,9 +3338,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,41 +3380,44 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>44957</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44592</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43861</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43496</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43131</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42766</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3236,36 +3427,39 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>637500</v>
+      </c>
+      <c r="E81" s="3">
         <v>103700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1375100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>671500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21800</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3469,12 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,35 +3490,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>104500</v>
+      </c>
+      <c r="E83" s="3">
         <v>82300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>48200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,9 +3529,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,36 +3739,39 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1598800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1290300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1605300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1471200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>151900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>51300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3565,9 +3781,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,35 +3802,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-132600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-80000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,9 +3841,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,36 +3925,39 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1183700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-318300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2859100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1562400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-499500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-113400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,9 +3967,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,36 +4153,39 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-936900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>34100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2050300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>615700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100300</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3950,18 +4195,21 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8100</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3977,8 +4225,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3989,36 +4237,39 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>465100</v>
+      </c>
+      <c r="E102" s="3">
         <v>26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1219800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1959000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>268100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>29100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-97900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>106800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,7 +4279,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>ZM</t>
   </si>
@@ -952,16 +952,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>125500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+        <v>-36800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-43800</v>
       </c>
       <c r="G14" s="3">
-        <v>9800</v>
+        <v>-2500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -994,25 +994,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>104500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>16400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4001900</v>
+        <v>3929000</v>
       </c>
       <c r="E17" s="3">
         <v>4147500</v>
@@ -1093,7 +1093,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>525300</v>
+        <v>598300</v>
       </c>
       <c r="E18" s="3">
         <v>245400</v>
@@ -1153,25 +1153,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>307000</v>
+        <v>-197300</v>
       </c>
       <c r="E20" s="3">
-        <v>3800</v>
+        <v>-41400</v>
       </c>
       <c r="F20" s="3">
-        <v>38000</v>
+        <v>5700</v>
       </c>
       <c r="G20" s="3">
-        <v>18200</v>
+        <v>-15600</v>
       </c>
       <c r="H20" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1300</v>
+        <v>-13700</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1195,25 +1195,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>936800</v>
+        <v>900000</v>
       </c>
       <c r="E21" s="3">
-        <v>331600</v>
+        <v>369200</v>
       </c>
       <c r="F21" s="3">
-        <v>1149800</v>
+        <v>1106100</v>
       </c>
       <c r="G21" s="3">
-        <v>706900</v>
+        <v>704400</v>
       </c>
       <c r="H21" s="3">
         <v>42800</v>
       </c>
       <c r="I21" s="3">
-        <v>15400</v>
+        <v>13200</v>
       </c>
       <c r="J21" s="3">
-        <v>-700</v>
+        <v>-2000</v>
       </c>
       <c r="K21" s="3">
         <v>1400</v>
@@ -1236,26 +1236,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1657,25 +1657,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-307000</v>
+        <v>197300</v>
       </c>
       <c r="E32" s="3">
-        <v>-3800</v>
+        <v>41400</v>
       </c>
       <c r="F32" s="3">
-        <v>-38000</v>
+        <v>-5700</v>
       </c>
       <c r="G32" s="3">
-        <v>-18200</v>
+        <v>15600</v>
       </c>
       <c r="H32" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
+        <v>13700</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -1705,19 +1705,19 @@
         <v>103700</v>
       </c>
       <c r="F33" s="3">
-        <v>1375100</v>
+        <v>1375600</v>
       </c>
       <c r="G33" s="3">
-        <v>671500</v>
+        <v>672300</v>
       </c>
       <c r="H33" s="3">
-        <v>21800</v>
+        <v>25300</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="J33" s="3">
-        <v>-8200</v>
+        <v>-3800</v>
       </c>
       <c r="K33" s="3">
         <v>-14400</v>
@@ -1789,19 +1789,19 @@
         <v>103700</v>
       </c>
       <c r="F35" s="3">
-        <v>1375100</v>
+        <v>1375600</v>
       </c>
       <c r="G35" s="3">
-        <v>671500</v>
+        <v>672300</v>
       </c>
       <c r="H35" s="3">
-        <v>21800</v>
+        <v>25300</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="J35" s="3">
-        <v>-8200</v>
+        <v>-3800</v>
       </c>
       <c r="K35" s="3">
         <v>-14400</v>
@@ -2033,26 +2033,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2076,25 +2076,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>427700</v>
+        <v>232500</v>
       </c>
       <c r="E45" s="3">
-        <v>386300</v>
+        <v>249700</v>
       </c>
       <c r="F45" s="3">
-        <v>344900</v>
+        <v>222000</v>
       </c>
       <c r="G45" s="3">
-        <v>253400</v>
+        <v>142300</v>
       </c>
       <c r="H45" s="3">
-        <v>119900</v>
+        <v>49000</v>
       </c>
       <c r="I45" s="3">
-        <v>36700</v>
+        <v>27400</v>
       </c>
       <c r="J45" s="3">
-        <v>19400</v>
+        <v>13900</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2160,19 +2160,19 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>435300</v>
+        <v>409200</v>
       </c>
       <c r="E47" s="3">
-        <v>491000</v>
+        <v>399000</v>
       </c>
       <c r="F47" s="3">
-        <v>423500</v>
+        <v>367800</v>
       </c>
       <c r="G47" s="3">
-        <v>41500</v>
+        <v>18700</v>
       </c>
       <c r="H47" s="3">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -2250,19 +2250,19 @@
         <v>179300</v>
       </c>
       <c r="F49" s="3">
-        <v>27600</v>
+        <v>51600</v>
       </c>
       <c r="G49" s="3">
         <v>24300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2370,25 +2370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>836100</v>
+        <v>61300</v>
       </c>
       <c r="E52" s="3">
-        <v>767600</v>
+        <v>121200</v>
       </c>
       <c r="F52" s="3">
-        <v>598100</v>
+        <v>82800</v>
       </c>
       <c r="G52" s="3">
-        <v>191700</v>
+        <v>55800</v>
       </c>
       <c r="H52" s="3">
-        <v>56600</v>
+        <v>17200</v>
       </c>
       <c r="I52" s="3">
-        <v>40600</v>
+        <v>11500</v>
       </c>
       <c r="J52" s="3">
-        <v>18800</v>
+        <v>2100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2574,19 +2574,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2616,25 +2616,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1752000</v>
+        <v>1332800</v>
       </c>
       <c r="E59" s="3">
-        <v>1724200</v>
+        <v>1368300</v>
       </c>
       <c r="F59" s="3">
-        <v>1571800</v>
+        <v>1241900</v>
       </c>
       <c r="G59" s="3">
-        <v>1251300</v>
+        <v>878300</v>
       </c>
       <c r="H59" s="3">
-        <v>332200</v>
+        <v>217300</v>
       </c>
       <c r="I59" s="3">
-        <v>147400</v>
+        <v>121800</v>
       </c>
       <c r="J59" s="3">
-        <v>65800</v>
+        <v>51700</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2700,19 +2700,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>48300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>73700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>85000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="I61" s="3">
         <v>14900</v>
@@ -2742,25 +2742,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>148200</v>
+        <v>81400</v>
       </c>
       <c r="E62" s="3">
-        <v>182800</v>
+        <v>67200</v>
       </c>
       <c r="F62" s="3">
-        <v>191600</v>
+        <v>68100</v>
       </c>
       <c r="G62" s="3">
-        <v>177300</v>
+        <v>61600</v>
       </c>
       <c r="H62" s="3">
-        <v>122100</v>
+        <v>36300</v>
       </c>
       <c r="I62" s="3">
-        <v>35300</v>
+        <v>24600</v>
       </c>
       <c r="J62" s="3">
-        <v>13600</v>
+        <v>9700</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3321,7 +3321,7 @@
         <v>833900</v>
       </c>
       <c r="I76" s="3">
-        <v>-7500</v>
+        <v>-7400</v>
       </c>
       <c r="J76" s="3">
         <v>-26700</v>
@@ -3443,19 +3443,19 @@
         <v>103700</v>
       </c>
       <c r="F81" s="3">
-        <v>1375100</v>
+        <v>1375600</v>
       </c>
       <c r="G81" s="3">
-        <v>671500</v>
+        <v>672300</v>
       </c>
       <c r="H81" s="3">
-        <v>21800</v>
+        <v>25300</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="J81" s="3">
-        <v>-8200</v>
+        <v>-3800</v>
       </c>
       <c r="K81" s="3">
         <v>-14400</v>
@@ -3497,10 +3497,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>104500</v>
+        <v>92000</v>
       </c>
       <c r="E83" s="3">
-        <v>82300</v>
+        <v>77000</v>
       </c>
       <c r="F83" s="3">
         <v>48200</v>

--- a/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ZM</t>
   </si>
@@ -656,58 +656,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44957</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44592</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43861</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43496</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43131</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42766</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,39 +718,42 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4665400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4527200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4393000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4099900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2651400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>622700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>330500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>151500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>60800</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -759,39 +763,42 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1129600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1070700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1100500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1054600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>822000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>115400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12500</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,39 +808,42 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3535800</v>
+      </c>
+      <c r="E10" s="3">
         <v>3456500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3292500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3045300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1829400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>507300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>269500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>120700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +875,39 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>852400</v>
+      </c>
+      <c r="E12" s="3">
         <v>783600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>774100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>363000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>164100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>67100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,27 +962,30 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-36800</v>
+        <v>-175800</v>
       </c>
       <c r="E14" s="3">
-        <v>37600</v>
+        <v>15700</v>
       </c>
       <c r="F14" s="3">
+        <v>45100</v>
+      </c>
+      <c r="G14" s="3">
         <v>-43800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,42 +1001,45 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E15" s="3">
         <v>104500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>82300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>28900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1029,9 +1052,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,38 +1071,39 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3929000</v>
+        <v>3850800</v>
       </c>
       <c r="E17" s="3">
-        <v>4147500</v>
+        <v>3876500</v>
       </c>
       <c r="F17" s="3">
+        <v>4140000</v>
+      </c>
+      <c r="G17" s="3">
         <v>3036300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1991500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>610000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>324400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>60800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,38 +1113,41 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>598300</v>
+        <v>814600</v>
       </c>
       <c r="E18" s="3">
-        <v>245400</v>
+        <v>650800</v>
       </c>
       <c r="F18" s="3">
+        <v>252900</v>
+      </c>
+      <c r="G18" s="3">
         <v>1063600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>659800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1128,9 +1158,12 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,38 +1180,39 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-325100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-197300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-41400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-13700</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1188,39 +1222,42 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>900000</v>
+        <v>1262400</v>
       </c>
       <c r="E21" s="3">
-        <v>369200</v>
+        <v>952500</v>
       </c>
       <c r="F21" s="3">
+        <v>376700</v>
+      </c>
+      <c r="G21" s="3">
         <v>1106100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>704400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>42800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,9 +1267,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1257,8 +1297,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1272,39 +1312,42 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1315600</v>
+      </c>
+      <c r="E23" s="3">
         <v>832300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>249300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1101600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>678000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,39 +1357,42 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>305300</v>
+      </c>
+      <c r="E24" s="3">
         <v>194900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>145600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-274000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,9 +1402,12 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,38 +1447,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E26" s="3">
         <v>637500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>103700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1375600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>672300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>25300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1440,39 +1492,42 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E27" s="3">
         <v>637500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>103700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1375100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>671500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21800</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14400</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1537,12 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,39 +1717,42 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E32" s="3">
         <v>197300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>41400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>13700</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,39 +1762,42 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E33" s="3">
         <v>637500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>103700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1375600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>672300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14400</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,9 +1807,12 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,39 +1852,42 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E35" s="3">
         <v>637500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>103700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1375600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>672300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14400</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,44 +1897,47 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44957</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44592</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43861</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43496</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43131</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42766</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,9 +1947,12 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,35 +1988,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1349400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1558300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1086800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1062800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2240300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>283100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>63600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,36 +2030,39 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6442300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5404200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4325800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4356400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2004400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>572100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>112800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>103100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,36 +2075,39 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>495200</v>
+      </c>
+      <c r="E43" s="3">
         <v>536100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>557400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>419700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>294700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24500</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2120,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,8 +2150,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2069,36 +2165,39 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>210100</v>
+      </c>
+      <c r="E45" s="3">
         <v>232500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>249700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>222000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,36 +2210,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8676000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7926200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6356400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6183800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4792900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1095500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>276700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>183200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,30 +2255,33 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>591500</v>
+      </c>
+      <c r="E47" s="3">
         <v>409200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>399000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>367800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,39 +2297,42 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>386400</v>
+      </c>
+      <c r="E48" s="3">
         <v>352700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>333700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>318300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>247600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>125700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,35 +2345,38 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>365900</v>
+      </c>
+      <c r="E49" s="3">
         <v>379500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>179300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>51600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2200</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2273,15 +2384,18 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,36 +2480,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E52" s="3">
         <v>61300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>121200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>82800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2525,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,36 +2570,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10988400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9929800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8128100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7551300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5298000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1289800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>354600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>215000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,9 +2615,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,35 +2656,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,30 +2698,33 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E58" s="3">
         <v>24600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2609,36 +2743,39 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1432600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1332800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1368300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1241900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>878300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>217300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>121800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>51700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,36 +2788,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1903300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1762200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1738600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1579700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1260000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>333800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>152300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68500</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,33 +2833,36 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E61" s="3">
         <v>48300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>73700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>85000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>90400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>64800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14900</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2735,36 +2878,39 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E62" s="3">
         <v>81400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>67200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>61600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9700</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2923,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,36 +3058,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2053300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1910400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1921500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1771300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1437200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>455900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>202500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3103,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3069,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>159600</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>159600</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>159600</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3089,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,36 +3302,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3799500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2789300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2151800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2048100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>672500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-25200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-32700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3347,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,36 +3482,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8935100</v>
+      </c>
+      <c r="E76" s="3">
         <v>8019400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6206600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5780000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3860800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>833900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-7400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-26700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,9 +3527,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,44 +3572,47 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44957</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44592</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43861</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43496</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43131</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42766</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3430,39 +3622,42 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1010200</v>
+      </c>
+      <c r="E81" s="3">
         <v>637500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>103700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1375600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>672300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14400</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,9 +3667,12 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3689,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E83" s="3">
         <v>92000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3731,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,39 +3956,42 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1945300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1598800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1290300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1605300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1471200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>151900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3784,9 +4001,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,38 +4023,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-136600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-103800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-132600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-80000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,9 +4065,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,39 +4155,42 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1106000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1183700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-318300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2859100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1562400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-499500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-113400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3970,9 +4200,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,39 +4399,42 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1028100</v>
+      </c>
+      <c r="E100" s="3">
         <v>60200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-936900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>34100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2050300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>615700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100300</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,21 +4444,24 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4228,8 +4477,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4240,39 +4489,42 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E102" s="3">
         <v>465100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1219800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1959000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>268100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-97900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>106800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,7 +4534,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>ZM</t>
   </si>
@@ -656,62 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44592</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43861</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43496</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43131</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42766</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,42 +721,45 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4868800</v>
+      </c>
+      <c r="E8" s="3">
         <v>4665400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4527200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4393000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4099900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2651400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>622700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>330500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>151500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>60800</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -766,42 +769,45 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1100800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1129600</v>
       </c>
-      <c r="E9" s="3">
-        <v>1070700</v>
-      </c>
       <c r="F9" s="3">
+        <v>1077800</v>
+      </c>
+      <c r="G9" s="3">
         <v>1100500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1054600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>822000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>115400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,42 +817,45 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3767900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3535800</v>
       </c>
-      <c r="E10" s="3">
-        <v>3456500</v>
-      </c>
       <c r="F10" s="3">
+        <v>3449400</v>
+      </c>
+      <c r="G10" s="3">
         <v>3292500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3045300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1829400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>507300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>269500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>120700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,41 +888,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>844900</v>
+      </c>
+      <c r="E12" s="3">
         <v>852400</v>
       </c>
-      <c r="E12" s="3">
-        <v>783600</v>
-      </c>
       <c r="F12" s="3">
+        <v>803200</v>
+      </c>
+      <c r="G12" s="3">
         <v>774100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>363000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>164100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>67100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,30 +981,33 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-951600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-175800</v>
       </c>
-      <c r="E14" s="3">
-        <v>15700</v>
-      </c>
       <c r="F14" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="G14" s="3">
         <v>45100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-43800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,45 +1023,48 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E15" s="3">
         <v>122600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>104500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>82300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>28900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,41 +1097,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3726900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3850800</v>
       </c>
-      <c r="E17" s="3">
-        <v>3876500</v>
-      </c>
       <c r="F17" s="3">
+        <v>3949400</v>
+      </c>
+      <c r="G17" s="3">
         <v>4140000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3036300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1991500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>610000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>324400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>156300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>60800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,41 +1142,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1141800</v>
+      </c>
+      <c r="E18" s="3">
         <v>814600</v>
       </c>
-      <c r="E18" s="3">
-        <v>650800</v>
-      </c>
       <c r="F18" s="3">
+        <v>577800</v>
+      </c>
+      <c r="G18" s="3">
         <v>252900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1063600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>659800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1161,9 +1190,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,41 +1213,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-325100</v>
+        <v>-11600</v>
       </c>
       <c r="E20" s="3">
-        <v>-197300</v>
+        <v>15300</v>
       </c>
       <c r="F20" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-41400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13700</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,42 +1258,45 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1262400</v>
+        <v>1286200</v>
       </c>
       <c r="E21" s="3">
-        <v>952500</v>
+        <v>922000</v>
       </c>
       <c r="F21" s="3">
+        <v>669500</v>
+      </c>
+      <c r="G21" s="3">
         <v>376700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1106100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>704400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>42800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,9 +1306,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1300,8 +1339,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1315,42 +1354,45 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2422300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1315600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>832300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>249300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1101600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>678000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>8300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,42 +1402,45 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>522100</v>
+      </c>
+      <c r="E24" s="3">
         <v>305300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>194900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>145600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-274000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,9 +1450,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,41 +1498,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1900100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1010200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>637500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>103700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1375600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>672300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>25300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1495,42 +1546,45 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1900200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1010200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>637500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>103700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1375100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>671500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21800</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,9 +1594,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,42 +1786,45 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>325100</v>
+        <v>11600</v>
       </c>
       <c r="E32" s="3">
-        <v>197300</v>
+        <v>-15300</v>
       </c>
       <c r="F32" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="G32" s="3">
         <v>41400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13700</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,42 +1834,45 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1900100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1010200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>637500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>103700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1375600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>672300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>25300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,9 +1882,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,42 +1930,45 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1900100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1010200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>637500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>103700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1375600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>672300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>25300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,47 +1978,50 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44592</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43861</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43496</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43131</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42766</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1950,9 +2031,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,38 +2074,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1272900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1349400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1558300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1086800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1062800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2240300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>283100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,39 +2119,42 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6544000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6442300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5404200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4325800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4356400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2004400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>572100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>112800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>103100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,39 +2167,42 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>497300</v>
+      </c>
+      <c r="E43" s="3">
         <v>495200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>536100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>557400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>419700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>294700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,9 +2215,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2153,8 +2248,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2168,39 +2263,42 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E45" s="3">
         <v>210100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>232500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>249700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>222000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>142300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2213,39 +2311,42 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8658000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8676000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7926200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6356400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6183800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4792900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1095500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>276700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>183200</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2258,33 +2359,36 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1578600</v>
+      </c>
+      <c r="E47" s="3">
         <v>591500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>409200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>399000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>367800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2300,42 +2404,45 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>316900</v>
+      </c>
+      <c r="E48" s="3">
         <v>386400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>352700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>333700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>318300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>247600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>125700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2348,38 +2455,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>471600</v>
+      </c>
+      <c r="E49" s="3">
         <v>365900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>379500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>179300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>51600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2387,15 +2497,18 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,39 +2599,42 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E52" s="3">
         <v>95400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>121200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>82800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,9 +2647,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,39 +2695,42 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11960400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10988400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9929800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8128100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7551300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5298000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1289800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>354600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>215000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,9 +2743,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,38 +2786,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,33 +2831,36 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E58" s="3">
         <v>27000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2746,39 +2879,42 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1524400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1432600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1332800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1368300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1241900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>878300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>217300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>121800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,39 +2927,42 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1999200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1903300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1762200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1738600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1579700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1260000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>333800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>152300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>68500</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,36 +2975,39 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E61" s="3">
         <v>37400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>73700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>85000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>90400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>64800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2881,39 +3023,42 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E62" s="3">
         <v>95400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>81400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>67200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,9 +3071,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,39 +3215,42 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2152200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2053300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1910400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1921500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1771300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1437200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>455900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>202500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,9 +3263,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3240,13 +3407,13 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>159600</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>159600</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>159600</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,39 +3475,42 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5699700</v>
+      </c>
+      <c r="E72" s="3">
         <v>3799500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2789300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2151800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2048100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>672500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,9 +3523,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,39 +3667,42 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9808300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8935100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8019400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6206600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5780000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3860800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>833900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-7400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-26700</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,9 +3715,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,47 +3763,50 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44592</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43861</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43496</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43131</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42766</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3625,42 +3816,45 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1900100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1010200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>637500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>103700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1375600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>672300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>25300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,9 +3864,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,41 +3887,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E83" s="3">
         <v>109100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>92000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>48200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,9 +3932,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,42 +4172,45 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1989000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1945300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1598800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1290300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1605300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1471200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>151900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>51300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9400</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,9 +4220,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,41 +4243,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-65000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-136600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-103800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-132600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-80000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,9 +4288,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,42 +4384,45 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-278900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1106000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1183700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-318300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2859100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1562400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-499500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-113400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4203,9 +4432,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,42 +4644,45 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1805400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1028100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>60200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-936900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>34100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2050300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>615700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100300</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,24 +4692,27 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4480,8 +4728,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4492,42 +4740,45 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-204000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>465100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1219800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1959000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>268100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>29100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-97900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>106800</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4537,7 +4788,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
